--- a/notebooks/rda-experiments/runs/v13-sample3/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v13-sample3/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="182">
   <si>
     <t>fields in reference</t>
   </si>
@@ -1049,31 +1049,31 @@
         <v>102</v>
       </c>
       <c r="D4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H4">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="I4">
-        <v>0.646</v>
+        <v>0.664</v>
       </c>
       <c r="J4">
-        <v>0.4952380952380953</v>
+        <v>0.5096153846153846</v>
       </c>
       <c r="K4">
-        <v>0.4761904761904762</v>
+        <v>0.4711538461538461</v>
       </c>
       <c r="L4">
-        <v>0.02857142857142857</v>
+        <v>0.01923076923076923</v>
       </c>
     </row>
   </sheetData>
@@ -3946,7 +3946,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4322,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
@@ -4339,7 +4339,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
@@ -4359,7 +4359,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
         <v>42</v>
@@ -4376,7 +4376,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>43</v>
@@ -4396,7 +4396,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>44</v>
@@ -4405,13 +4405,13 @@
         <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F24" t="s">
         <v>142</v>
       </c>
       <c r="G24" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4419,7 +4419,7 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C25" t="s">
         <v>45</v>
@@ -4436,7 +4436,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
         <v>46</v>
@@ -4456,7 +4456,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
         <v>47</v>
@@ -4473,7 +4473,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
@@ -4493,7 +4493,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
         <v>49</v>
@@ -4510,7 +4510,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
         <v>50</v>
@@ -4530,7 +4530,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>51</v>
@@ -4539,13 +4539,10 @@
         <v>178</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F31" t="s">
-        <v>142</v>
-      </c>
-      <c r="G31" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4553,7 +4550,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
         <v>52</v>
@@ -4570,7 +4567,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
         <v>53</v>
@@ -5939,10 +5936,10 @@
         <v>3</v>
       </c>
       <c r="B104" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E104" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F104" t="s">
         <v>143</v>
@@ -5953,26 +5950,12 @@
         <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E105" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F105" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106">
-        <v>3</v>
-      </c>
-      <c r="B106" t="s">
-        <v>105</v>
-      </c>
-      <c r="E106" t="s">
-        <v>140</v>
-      </c>
-      <c r="F106" t="s">
         <v>143</v>
       </c>
     </row>
@@ -5983,7 +5966,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -9663,7 +9646,7 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D169" t="s">
         <v>40</v>
@@ -9683,7 +9666,7 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D170" t="s">
         <v>41</v>
@@ -9706,7 +9689,7 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D171" t="s">
         <v>42</v>
@@ -9726,7 +9709,7 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D172" t="s">
         <v>43</v>
@@ -9749,7 +9732,7 @@
         <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D173" t="s">
         <v>44</v>
@@ -9758,13 +9741,13 @@
         <v>177</v>
       </c>
       <c r="F173" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G173" t="s">
         <v>142</v>
       </c>
       <c r="H173" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -9775,7 +9758,7 @@
         <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D174" t="s">
         <v>45</v>
@@ -9795,7 +9778,7 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D175" t="s">
         <v>46</v>
@@ -9818,7 +9801,7 @@
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D176" t="s">
         <v>47</v>
@@ -9838,7 +9821,7 @@
         <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D177" t="s">
         <v>48</v>
@@ -9861,7 +9844,7 @@
         <v>14</v>
       </c>
       <c r="C178" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D178" t="s">
         <v>49</v>
@@ -9881,7 +9864,7 @@
         <v>14</v>
       </c>
       <c r="C179" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D179" t="s">
         <v>50</v>
@@ -9904,7 +9887,7 @@
         <v>14</v>
       </c>
       <c r="C180" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D180" t="s">
         <v>51</v>
@@ -9913,13 +9896,10 @@
         <v>178</v>
       </c>
       <c r="F180" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G180" t="s">
-        <v>142</v>
-      </c>
-      <c r="H180" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -9930,7 +9910,7 @@
         <v>14</v>
       </c>
       <c r="C181" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D181" t="s">
         <v>52</v>
@@ -9950,7 +9930,7 @@
         <v>14</v>
       </c>
       <c r="C182" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D182" t="s">
         <v>53</v>
@@ -11532,10 +11512,10 @@
         <v>14</v>
       </c>
       <c r="C253" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="F253" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G253" t="s">
         <v>143</v>
@@ -11549,29 +11529,12 @@
         <v>14</v>
       </c>
       <c r="C254" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F254" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G254" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8">
-      <c r="A255">
-        <v>3</v>
-      </c>
-      <c r="B255" t="s">
-        <v>14</v>
-      </c>
-      <c r="C255" t="s">
-        <v>105</v>
-      </c>
-      <c r="F255" t="s">
-        <v>140</v>
-      </c>
-      <c r="G255" t="s">
         <v>143</v>
       </c>
     </row>
